--- a/survey_templates/040_social_media_ethics_assessment--survey_templates.xlsx
+++ b/survey_templates/040_social_media_ethics_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_ignore_it'}</t>
+          <t>i_ignore_it</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I ignore it'}</t>
+          <t>I ignore it</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_respond_with_a_kind_message'}</t>
+          <t>i_respond_with_a_kind_message</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I respond with a kind message'}</t>
+          <t>I respond with a kind message</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'i_block_or_limit_their_interactions'}</t>
+          <t>i_block_or_limit_their_interactions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'I block or limit their interactions'}</t>
+          <t>I block or limit their interactions</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'i_report_them'}</t>
+          <t>i_report_them</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'I report them'}</t>
+          <t>I report them</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"i_don't_share_anything"}</t>
+          <t>i_don't_share_anything</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "I don't share anything"}</t>
+          <t>I don't share anything</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_share_only_with_close_friends'}</t>
+          <t>i_share_only_with_close_friends</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I share only with close friends'}</t>
+          <t>I share only with close friends</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'i_share_with_anyone'}</t>
+          <t>i_share_with_anyone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'I share with anyone'}</t>
+          <t>I share with anyone</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_use_strong_passwords_and_two-factor_authentication'}</t>
+          <t>i_use_strong_passwords_and_two-factor_authentication</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I use strong passwords and two-factor authentication'}</t>
+          <t>I use strong passwords and two-factor authentication</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_use_a_separate_email_address_and_phone_number_for_social_media'}</t>
+          <t>i_use_a_separate_email_address_and_phone_number_for_social_media</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I use a separate email address and phone number for social media'}</t>
+          <t>I use a separate email address and phone number for social media</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat important'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very important'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_very_confident'}</t>
+          <t>not_very_confident</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not very confident'}</t>
+          <t>Not very confident</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_confident'}</t>
+          <t>somewhat_confident</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat confident'}</t>
+          <t>Somewhat confident</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_confident'}</t>
+          <t>very_confident</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very confident'}</t>
+          <t>Very confident</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_only_post_it_with_close_friends'}</t>
+          <t>i_only_post_it_with_close_friends</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I only post it with close friends'}</t>
+          <t>I only post it with close friends</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_only_post_it_with_trusted_people'}</t>
+          <t>i_only_post_it_with_trusted_people</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I only post it with trusted people'}</t>
+          <t>I only post it with trusted people</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'i_post_it_publicly'}</t>
+          <t>i_post_it_publicly</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'I post it publicly'}</t>
+          <t>I post it publicly</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not very important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat important'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very important'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
